--- a/Dependencies/Ping_2018/fc/dataset_metrics.xlsx
+++ b/Dependencies/Ping_2018/fc/dataset_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,77 +458,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fcb2</t>
+          <t>fcb1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57123</v>
+        <v>62697</v>
       </c>
       <c r="C2" t="n">
-        <v>46909</v>
+        <v>52093</v>
       </c>
       <c r="D2" t="n">
-        <v>46706</v>
+        <v>51888</v>
       </c>
       <c r="E2" t="n">
-        <v>8878</v>
+        <v>9848</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fcb3</t>
+          <t>fcb2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58749</v>
+        <v>57476</v>
       </c>
       <c r="C3" t="n">
-        <v>46669</v>
+        <v>46951</v>
       </c>
       <c r="D3" t="n">
-        <v>46437</v>
+        <v>46802</v>
       </c>
       <c r="E3" t="n">
-        <v>8673</v>
+        <v>8857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fcb4</t>
+          <t>fcb3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70896</v>
+        <v>55302</v>
       </c>
       <c r="C4" t="n">
-        <v>58690</v>
+        <v>44672</v>
       </c>
       <c r="D4" t="n">
-        <v>58472</v>
+        <v>44438</v>
       </c>
       <c r="E4" t="n">
-        <v>11188</v>
+        <v>8290</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>fcb4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70859</v>
+      </c>
+      <c r="C5" t="n">
+        <v>59433</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59263</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11321</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>fcb5</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>58151</v>
-      </c>
-      <c r="C5" t="n">
-        <v>43933</v>
-      </c>
-      <c r="D5" t="n">
-        <v>43740</v>
-      </c>
-      <c r="E5" t="n">
-        <v>8174</v>
+      <c r="B6" t="n">
+        <v>55144</v>
+      </c>
+      <c r="C6" t="n">
+        <v>42233</v>
+      </c>
+      <c r="D6" t="n">
+        <v>42083</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7836</v>
       </c>
     </row>
   </sheetData>

--- a/Dependencies/Ping_2018/fc/dataset_metrics.xlsx
+++ b/Dependencies/Ping_2018/fc/dataset_metrics.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62697</v>
+        <v>131555</v>
       </c>
       <c r="C2" t="n">
-        <v>52093</v>
+        <v>73129</v>
       </c>
       <c r="D2" t="n">
-        <v>51888</v>
+        <v>73129</v>
       </c>
       <c r="E2" t="n">
-        <v>9848</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57476</v>
+        <v>127955</v>
       </c>
       <c r="C3" t="n">
-        <v>46951</v>
+        <v>68635</v>
       </c>
       <c r="D3" t="n">
-        <v>46802</v>
+        <v>68635</v>
       </c>
       <c r="E3" t="n">
-        <v>8857</v>
+        <v>13159</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55302</v>
+        <v>121410</v>
       </c>
       <c r="C4" t="n">
-        <v>44672</v>
+        <v>65132</v>
       </c>
       <c r="D4" t="n">
-        <v>44438</v>
+        <v>65132</v>
       </c>
       <c r="E4" t="n">
-        <v>8290</v>
+        <v>12418</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70859</v>
+        <v>147136</v>
       </c>
       <c r="C5" t="n">
-        <v>59433</v>
+        <v>81523</v>
       </c>
       <c r="D5" t="n">
-        <v>59263</v>
+        <v>81523</v>
       </c>
       <c r="E5" t="n">
-        <v>11321</v>
+        <v>15806</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55144</v>
+        <v>114870</v>
       </c>
       <c r="C6" t="n">
-        <v>42233</v>
+        <v>59681</v>
       </c>
       <c r="D6" t="n">
-        <v>42083</v>
+        <v>59681</v>
       </c>
       <c r="E6" t="n">
-        <v>7836</v>
+        <v>11333</v>
       </c>
     </row>
   </sheetData>
